--- a/excel/Crowdpear.xlsx
+++ b/excel/Crowdpear.xlsx
@@ -8,39 +8,40 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Crowdpear\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EEFEA5-F194-4BD4-A1B9-42C74159CF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F826D2-793E-4E81-9612-5D8917E7E5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="12" r:id="rId2"/>
-    <sheet name="Užnerio butai XV" sheetId="28" r:id="rId3"/>
-    <sheet name="Vakaro 3A K1 III" sheetId="27" r:id="rId4"/>
-    <sheet name="Kauno 36-118 II" sheetId="26" r:id="rId5"/>
-    <sheet name="Tautvilo kotedžai XIV" sheetId="24" r:id="rId6"/>
-    <sheet name="Horizonto 2A XII" sheetId="25" r:id="rId7"/>
-    <sheet name="Žemoji 52 XXIX“" sheetId="23" r:id="rId8"/>
-    <sheet name="Namas Panevėžyje" sheetId="22" r:id="rId9"/>
-    <sheet name="Vanagupės 36A-204 II" sheetId="21" r:id="rId10"/>
-    <sheet name="Vingio namai XIV" sheetId="20" r:id="rId11"/>
-    <sheet name="Druskonio perlai VII" sheetId="19" r:id="rId12"/>
-    <sheet name="Birelių namas II" sheetId="18" r:id="rId13"/>
-    <sheet name="Sūduvos 8-2" sheetId="17" r:id="rId14"/>
-    <sheet name="Miškininkų 30 II" sheetId="16" r:id="rId15"/>
-    <sheet name="Pagojo 1 II" sheetId="15" r:id="rId16"/>
-    <sheet name="Vienbutis Minsko 5A" sheetId="14" r:id="rId17"/>
-    <sheet name="Dvibutis Sodybų 12" sheetId="13" r:id="rId18"/>
-    <sheet name="Sfintii Arhangheli 21" sheetId="11" r:id="rId19"/>
-    <sheet name="Girinaičių 7 II" sheetId="10" r:id="rId20"/>
-    <sheet name="Girios 112 II" sheetId="9" r:id="rId21"/>
-    <sheet name="Piliarožių 10 VI" sheetId="8" r:id="rId22"/>
-    <sheet name="Girinaičių 7" sheetId="7" r:id="rId23"/>
-    <sheet name="Kauno 36-232" sheetId="6" r:id="rId24"/>
-    <sheet name="Sodziaus 7A (1)" sheetId="5" r:id="rId25"/>
-    <sheet name="Sodziaus 7A" sheetId="4" r:id="rId26"/>
-    <sheet name="Pušynas VII" sheetId="3" r:id="rId27"/>
-    <sheet name="Užnerio butai III" sheetId="2" r:id="rId28"/>
+    <sheet name="Vienbutis Gilužiuose III" sheetId="29" r:id="rId3"/>
+    <sheet name="Užnerio butai XV" sheetId="28" r:id="rId4"/>
+    <sheet name="Vakaro 3A K1 III" sheetId="27" r:id="rId5"/>
+    <sheet name="Kauno 36-118 II" sheetId="26" r:id="rId6"/>
+    <sheet name="Tautvilo kotedžai XIV" sheetId="24" r:id="rId7"/>
+    <sheet name="Horizonto 2A XII" sheetId="25" r:id="rId8"/>
+    <sheet name="Žemoji 52 XXIX“" sheetId="23" r:id="rId9"/>
+    <sheet name="Namas Panevėžyje" sheetId="22" r:id="rId10"/>
+    <sheet name="Vanagupės 36A-204 II" sheetId="21" r:id="rId11"/>
+    <sheet name="Vingio namai XIV" sheetId="20" r:id="rId12"/>
+    <sheet name="Druskonio perlai VII" sheetId="19" r:id="rId13"/>
+    <sheet name="Birelių namas II" sheetId="18" r:id="rId14"/>
+    <sheet name="Sūduvos 8-2" sheetId="17" r:id="rId15"/>
+    <sheet name="Miškininkų 30 II" sheetId="16" r:id="rId16"/>
+    <sheet name="Pagojo 1 II" sheetId="15" r:id="rId17"/>
+    <sheet name="Vienbutis Minsko 5A" sheetId="14" r:id="rId18"/>
+    <sheet name="Dvibutis Sodybų 12" sheetId="13" r:id="rId19"/>
+    <sheet name="Sfintii Arhangheli 21" sheetId="11" r:id="rId20"/>
+    <sheet name="Girinaičių 7 II" sheetId="10" r:id="rId21"/>
+    <sheet name="Girios 112 II" sheetId="9" r:id="rId22"/>
+    <sheet name="Piliarožių 10 VI" sheetId="8" r:id="rId23"/>
+    <sheet name="Girinaičių 7" sheetId="7" r:id="rId24"/>
+    <sheet name="Kauno 36-232" sheetId="6" r:id="rId25"/>
+    <sheet name="Sodziaus 7A (1)" sheetId="5" r:id="rId26"/>
+    <sheet name="Sodziaus 7A" sheetId="4" r:id="rId27"/>
+    <sheet name="Pušynas VII" sheetId="3" r:id="rId28"/>
+    <sheet name="Užnerio butai III" sheetId="2" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="104">
   <si>
     <t>Paskola</t>
   </si>
@@ -370,16 +371,21 @@
   <si>
     <t>Investuota, Eur</t>
   </si>
+  <si>
+    <t>Vienbutis Gilužiuose III</t>
+  </si>
+  <si>
+    <t>LT-591</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="yyyy\.mm\.dd;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -528,7 +534,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -584,9 +590,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -599,9 +602,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -630,7 +630,35 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="106">
+  <dxfs count="112">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1373,6 +1401,20 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1387,6 +1429,622 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35E485D7-B2BA-42C6-937A-900E9A1FA5AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B2E05F0-3B0A-43F4-87A0-0AAA040BEF63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFF1A2E9-B58F-4E36-B448-FD6ECF70125D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FA0BF96-2C5B-4B6E-B63C-C975C26B2C7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26D0705A-5DD9-4DA0-8162-F093A90BCD47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{139E4DE8-C656-4C9C-831B-83B7F673283D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7623111-2B0A-45C7-8958-A3A45FB4FC72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1801AA9F-E704-4CC3-8A89-B66D72DFC4C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6372A822-4C00-4A7A-937E-530CE05BA463}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E16569F-6987-4A44-B7D7-EF1FB29482A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4B638E9-59DE-4707-9ADC-5DDFC65BBD0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47625" y="3648075"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1442,511 +2100,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFF1A2E9-B58F-4E36-B448-FD6ECF70125D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FA0BF96-2C5B-4B6E-B63C-C975C26B2C7A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26D0705A-5DD9-4DA0-8162-F093A90BCD47}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{139E4DE8-C656-4C9C-831B-83B7F673283D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7623111-2B0A-45C7-8958-A3A45FB4FC72}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1801AA9F-E704-4CC3-8A89-B66D72DFC4C4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6372A822-4C00-4A7A-937E-530CE05BA463}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E16569F-6987-4A44-B7D7-EF1FB29482A6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4B638E9-59DE-4707-9ADC-5DDFC65BBD0C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2002,63 +2156,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63180A35-B029-446C-8428-2E9EA9360DFC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2114,7 +2212,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2170,7 +2268,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2226,7 +2324,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2282,7 +2380,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2338,7 +2436,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2394,7 +2492,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2467,11 +2565,11 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A229A8B-F3F3-4BE1-8727-DC7A2B21128C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63180A35-B029-446C-8428-2E9EA9360DFC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2527,6 +2625,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A229A8B-F3F3-4BE1-8727-DC7A2B21128C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35C2F4B5-CAB1-47E1-8A73-CBE8F66DB2EB}"/>
             </a:ext>
           </a:extLst>
@@ -2562,7 +2716,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2618,7 +2772,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2674,7 +2828,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2730,7 +2884,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2774,62 +2928,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B2E05F0-3B0A-43F4-87A0-0AAA040BEF63}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="47625" y="3648075"/>
           <a:ext cx="914400" cy="914400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3105,7 +3203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -3119,39 +3217,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="32" t="s">
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="O1" s="32" t="s">
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="O1" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="33" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33" t="s">
+      <c r="T1" s="31"/>
+      <c r="U1" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -3235,7 +3333,7 @@
         <f>'Užnerio butai III'!B3</f>
         <v>45719</v>
       </c>
-      <c r="C3" s="22" t="str">
+      <c r="C3" s="21" t="str">
         <f>'Užnerio butai III'!B2</f>
         <v>Užnerio butai III</v>
       </c>
@@ -3255,11 +3353,11 @@
         <f>'Užnerio butai III'!B11</f>
         <v>100</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="11">
         <f>'Užnerio butai III'!B12</f>
         <v>46087</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="11">
         <f>'Užnerio butai III'!R3</f>
         <v>46091</v>
       </c>
@@ -3285,7 +3383,7 @@
       </c>
       <c r="P3" s="4">
         <f>SUM(G3:G200)-S3</f>
-        <v>1186.4799999999998</v>
+        <v>1191.8300000000002</v>
       </c>
       <c r="Q3" s="4">
         <f>Pinigai!H2</f>
@@ -3293,31 +3391,31 @@
       </c>
       <c r="R3" s="4">
         <f>U3-P3</f>
-        <v>0.22000000000025466</v>
+        <v>6.0099999999997635</v>
       </c>
       <c r="S3" s="4">
         <f>SUM(L3:L200)</f>
-        <v>1254.3300000000002</v>
+        <v>1377.57</v>
       </c>
       <c r="T3" s="4">
         <f>SUM(M3:M200)</f>
-        <v>116.69999999999999</v>
+        <v>127.84</v>
       </c>
       <c r="U3" s="4">
         <f>O3+T3+Q3</f>
-        <v>1186.7</v>
+        <v>1197.8399999999999</v>
       </c>
       <c r="V3" s="4">
         <f>U3-O3</f>
-        <v>156.70000000000005</v>
+        <v>167.83999999999992</v>
       </c>
       <c r="W3" s="14">
         <f>(U3-O3)/O3</f>
-        <v>0.15213592233009712</v>
+        <v>0.16295145631067953</v>
       </c>
       <c r="X3" s="14">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.12087267041206359</v>
+        <v>0.12084302306175232</v>
       </c>
       <c r="AC3" s="4" t="str">
         <f ca="1">'Užnerio butai III'!AA2</f>
@@ -3332,7 +3430,7 @@
         <f>'Pušynas VII'!B3</f>
         <v>45721</v>
       </c>
-      <c r="C4" s="22" t="str">
+      <c r="C4" s="21" t="str">
         <f>'Pušynas VII'!B2</f>
         <v>Pušynas VII</v>
       </c>
@@ -3352,11 +3450,11 @@
         <f>'Pušynas VII'!B11</f>
         <v>100</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="11">
         <f>'Pušynas VII'!B12</f>
         <v>46054</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="11">
         <f>'Pušynas VII'!R3</f>
         <v>46056</v>
       </c>
@@ -3389,7 +3487,7 @@
         <f>'Sodziaus 7A'!B3</f>
         <v>45725</v>
       </c>
-      <c r="C5" s="22" t="str">
+      <c r="C5" s="21" t="str">
         <f>'Sodziaus 7A'!B2</f>
         <v>Sodziaus 7A</v>
       </c>
@@ -3409,11 +3507,11 @@
         <f>'Sodziaus 7A'!B11</f>
         <v>100</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="11">
         <f>'Sodziaus 7A'!B12</f>
         <v>46005</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="11">
         <f>'Sodziaus 7A'!R3</f>
         <v>46049</v>
       </c>
@@ -3446,7 +3544,7 @@
         <f>'Sodziaus 7A (1)'!B3</f>
         <v>45729</v>
       </c>
-      <c r="C6" s="22" t="str">
+      <c r="C6" s="21" t="str">
         <f>'Sodziaus 7A (1)'!B2</f>
         <v>Sodziaus 7A</v>
       </c>
@@ -3466,11 +3564,11 @@
         <f>'Sodziaus 7A (1)'!B11</f>
         <v>10</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="11">
         <f>'Sodziaus 7A (1)'!B12</f>
         <v>46005</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="11">
         <f>'Sodziaus 7A (1)'!R3</f>
         <v>46049</v>
       </c>
@@ -3503,7 +3601,7 @@
         <f>'Kauno 36-232'!B3</f>
         <v>45743</v>
       </c>
-      <c r="C7" s="22" t="str">
+      <c r="C7" s="21" t="str">
         <f>'Kauno 36-232'!B2</f>
         <v>Kauno 36-232</v>
       </c>
@@ -3523,11 +3621,11 @@
         <f>'Kauno 36-232'!B11</f>
         <v>100</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="11">
         <f>'Kauno 36-232'!B12</f>
         <v>46112</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="11">
         <f>'Kauno 36-232'!R3</f>
         <v>46035</v>
       </c>
@@ -3560,7 +3658,7 @@
         <f>'Girinaičių 7'!B3</f>
         <v>45757</v>
       </c>
-      <c r="C8" s="22" t="str">
+      <c r="C8" s="21" t="str">
         <f>'Girinaičių 7'!B2</f>
         <v>Girinaičių 7</v>
       </c>
@@ -3580,11 +3678,11 @@
         <f>'Girinaičių 7'!B11</f>
         <v>100</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="11">
         <f>'Girinaičių 7'!B12</f>
         <v>45948</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="11">
         <f>'Girinaičių 7'!R3</f>
         <v>45911</v>
       </c>
@@ -3617,7 +3715,7 @@
         <f>'Piliarožių 10 VI'!B3</f>
         <v>45764</v>
       </c>
-      <c r="C9" s="22" t="str">
+      <c r="C9" s="21" t="str">
         <f>'Piliarožių 10 VI'!B2</f>
         <v>Piliarožių 10 VI</v>
       </c>
@@ -3637,11 +3735,11 @@
         <f>'Piliarožių 10 VI'!B11</f>
         <v>10</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="11">
         <f>'Piliarožių 10 VI'!B12</f>
         <v>46136</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="11">
         <f>'Piliarožių 10 VI'!R3</f>
         <v>46105</v>
       </c>
@@ -3674,7 +3772,7 @@
         <f>'Girios 112 II'!B3</f>
         <v>45770</v>
       </c>
-      <c r="C10" s="22" t="str">
+      <c r="C10" s="21" t="str">
         <f>'Girios 112 II'!B2</f>
         <v>Girios 112 II</v>
       </c>
@@ -3694,11 +3792,11 @@
         <f>'Girios 112 II'!B11</f>
         <v>100</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="11">
         <f>'Girios 112 II'!B12</f>
         <v>46140</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="11">
         <f>'Girios 112 II'!R3</f>
         <v>46073</v>
       </c>
@@ -3731,7 +3829,7 @@
         <f>'Girinaičių 7 II'!B3</f>
         <v>45791</v>
       </c>
-      <c r="C11" s="22" t="str">
+      <c r="C11" s="21" t="str">
         <f>'Girinaičių 7 II'!B2</f>
         <v>Girinaičių 7 II</v>
       </c>
@@ -3751,11 +3849,11 @@
         <f>'Girinaičių 7 II'!B11</f>
         <v>100</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="11">
         <f>'Girinaičių 7 II'!B12</f>
         <v>45975</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="11">
         <f>'Girinaičių 7 II'!R3</f>
         <v>45912</v>
       </c>
@@ -3788,7 +3886,7 @@
         <f>'Sfintii Arhangheli 21'!B3</f>
         <v>45908</v>
       </c>
-      <c r="C12" s="22" t="str">
+      <c r="C12" s="21" t="str">
         <f>'Sfintii Arhangheli 21'!B2</f>
         <v>Sfintii Arhangheli 21</v>
       </c>
@@ -3808,17 +3906,17 @@
         <f>'Sfintii Arhangheli 21'!B11</f>
         <v>123.24</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="11">
         <f>'Sfintii Arhangheli 21'!B12</f>
         <v>46274</v>
       </c>
-      <c r="I12" s="21" t="str">
+      <c r="I12" s="11">
         <f>'Sfintii Arhangheli 21'!R3</f>
-        <v/>
-      </c>
-      <c r="J12" s="10">
+        <v>46267</v>
+      </c>
+      <c r="J12" s="10" t="str">
         <f ca="1">'Sfintii Arhangheli 21'!B13</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="K12" s="10" t="str">
         <f ca="1">'Sfintii Arhangheli 21'!S3</f>
@@ -3826,11 +3924,11 @@
       </c>
       <c r="L12" s="4">
         <f>'Sfintii Arhangheli 21'!N3</f>
-        <v>0</v>
+        <v>123.24</v>
       </c>
       <c r="M12" s="4">
         <f>'Sfintii Arhangheli 21'!P3</f>
-        <v>10.510000000000002</v>
+        <v>12.740000000000002</v>
       </c>
       <c r="AC12" s="4" t="str">
         <f ca="1">'Sfintii Arhangheli 21'!AA2</f>
@@ -3845,7 +3943,7 @@
         <f>'Dvibutis Sodybų 12'!B3</f>
         <v>45912</v>
       </c>
-      <c r="C13" s="22" t="str">
+      <c r="C13" s="21" t="str">
         <f>'Dvibutis Sodybų 12'!B2</f>
         <v>Dvibutis Sodybų 12</v>
       </c>
@@ -3865,11 +3963,11 @@
         <f>'Dvibutis Sodybų 12'!B11</f>
         <v>100</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="11">
         <f>'Dvibutis Sodybų 12'!B12</f>
         <v>46098</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="11">
         <f>'Dvibutis Sodybų 12'!R3</f>
         <v>46084</v>
       </c>
@@ -3902,7 +4000,7 @@
         <f>'Vienbutis Minsko 5A'!B3</f>
         <v>45915</v>
       </c>
-      <c r="C14" s="22" t="str">
+      <c r="C14" s="21" t="str">
         <f>'Vienbutis Minsko 5A'!B2</f>
         <v>Vienbutis Minsko 5A</v>
       </c>
@@ -3922,21 +4020,21 @@
         <f>'Vienbutis Minsko 5A'!B11</f>
         <v>101.49</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="11">
         <f>'Vienbutis Minsko 5A'!B12</f>
         <v>46281</v>
       </c>
-      <c r="I14" s="21" t="str">
+      <c r="I14" s="11" t="str">
         <f>'Vienbutis Minsko 5A'!R3</f>
         <v/>
       </c>
       <c r="J14" s="10">
         <f ca="1">'Vienbutis Minsko 5A'!B13</f>
-        <v>16</v>
-      </c>
-      <c r="K14" s="10" t="str">
+        <v>-14</v>
+      </c>
+      <c r="K14" s="10">
         <f ca="1">'Vienbutis Minsko 5A'!S3</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="L14" s="4">
         <f>'Vienbutis Minsko 5A'!N3</f>
@@ -3948,7 +4046,7 @@
       </c>
       <c r="AC14" s="4" t="str">
         <f ca="1">'Vienbutis Minsko 5A'!AA2</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
@@ -3959,7 +4057,7 @@
         <f>'Pagojo 1 II'!B3</f>
         <v>45950</v>
       </c>
-      <c r="C15" s="22" t="str">
+      <c r="C15" s="21" t="str">
         <f>'Pagojo 1 II'!B2</f>
         <v>Pagojo 1 II</v>
       </c>
@@ -3979,11 +4077,11 @@
         <f>'Pagojo 1 II'!B11</f>
         <v>108.26</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="11">
         <f>'Pagojo 1 II'!B12</f>
         <v>46224</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="11">
         <f>'Pagojo 1 II'!R3</f>
         <v>46072</v>
       </c>
@@ -4016,7 +4114,7 @@
         <f>'Miškininkų 30 II'!B3</f>
         <v>45958</v>
       </c>
-      <c r="C16" s="22" t="str">
+      <c r="C16" s="21" t="str">
         <f>'Miškininkų 30 II'!B2</f>
         <v>Miškininkų 30 II</v>
       </c>
@@ -4036,17 +4134,17 @@
         <f>'Miškininkų 30 II'!B11</f>
         <v>10</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="11">
         <f>'Miškininkų 30 II'!B12</f>
         <v>46332</v>
       </c>
-      <c r="I16" s="21" t="str">
+      <c r="I16" s="11" t="str">
         <f>'Miškininkų 30 II'!R3</f>
         <v/>
       </c>
       <c r="J16" s="10">
         <f ca="1">'Miškininkų 30 II'!B13</f>
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="K16" s="10" t="str">
         <f ca="1">'Miškininkų 30 II'!S3</f>
@@ -4073,7 +4171,7 @@
         <f>'Sūduvos 8-2'!B3</f>
         <v>46003</v>
       </c>
-      <c r="C17" s="22" t="str">
+      <c r="C17" s="21" t="str">
         <f>'Sūduvos 8-2'!B2</f>
         <v>Sūduvos 8-2</v>
       </c>
@@ -4093,17 +4191,17 @@
         <f>'Sūduvos 8-2'!B11</f>
         <v>106.06</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="11">
         <f>'Sūduvos 8-2'!B12</f>
         <v>46371</v>
       </c>
-      <c r="I17" s="21" t="str">
+      <c r="I17" s="11" t="str">
         <f>'Sūduvos 8-2'!R3</f>
         <v/>
       </c>
       <c r="J17" s="10">
         <f ca="1">'Sūduvos 8-2'!B13</f>
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="K17" s="10" t="str">
         <f ca="1">'Sūduvos 8-2'!S3</f>
@@ -4130,7 +4228,7 @@
         <f>'Birelių namas II'!B3</f>
         <v>46010</v>
       </c>
-      <c r="C18" s="22" t="str">
+      <c r="C18" s="21" t="str">
         <f>'Birelių namas II'!B2</f>
         <v>Birelių namas II</v>
       </c>
@@ -4150,17 +4248,17 @@
         <f>'Birelių namas II'!B11</f>
         <v>10</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="11">
         <f>'Birelių namas II'!B12</f>
         <v>46378</v>
       </c>
-      <c r="I18" s="21" t="str">
+      <c r="I18" s="11" t="str">
         <f>'Birelių namas II'!R3</f>
         <v/>
       </c>
       <c r="J18" s="10">
         <f ca="1">'Birelių namas II'!B13</f>
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="K18" s="10" t="str">
         <f ca="1">'Birelių namas II'!S3</f>
@@ -4172,7 +4270,7 @@
       </c>
       <c r="M18" s="4">
         <f>'Birelių namas II'!P3</f>
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="AC18" s="4" t="str">
         <f ca="1">'Birelių namas II'!AA2</f>
@@ -4187,7 +4285,7 @@
         <f>'Druskonio perlai VII'!B3</f>
         <v>46035</v>
       </c>
-      <c r="C19" s="22" t="str">
+      <c r="C19" s="21" t="str">
         <f>'Druskonio perlai VII'!B2</f>
         <v>Druskonio perlai VII</v>
       </c>
@@ -4207,11 +4305,11 @@
         <f>'Druskonio perlai VII'!B11</f>
         <v>118.77</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="11">
         <f>'Druskonio perlai VII'!B12</f>
         <v>46408</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="11">
         <f>'Druskonio perlai VII'!R3</f>
         <v>46086</v>
       </c>
@@ -4244,7 +4342,7 @@
         <f>'Vingio namai XIV'!B3</f>
         <v>46049</v>
       </c>
-      <c r="C20" s="23" t="str">
+      <c r="C20" s="22" t="str">
         <f>'Vingio namai XIV'!B2</f>
         <v>Vingio namai XIV</v>
       </c>
@@ -4264,17 +4362,17 @@
         <f>'Vingio namai XIV'!B11</f>
         <v>123.63</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="11">
         <f>'Vingio namai XIV'!B12</f>
         <v>46420</v>
       </c>
-      <c r="I20" s="21" t="str">
+      <c r="I20" s="11" t="str">
         <f>'Vingio namai XIV'!R3</f>
         <v/>
       </c>
       <c r="J20" s="10">
         <f ca="1">'Vingio namai XIV'!B13</f>
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="K20" s="10" t="str">
         <f ca="1">'Vingio namai XIV'!S3</f>
@@ -4286,7 +4384,7 @@
       </c>
       <c r="M20" s="4">
         <f>'Vingio namai XIV'!P3</f>
-        <v>4.05</v>
+        <v>6.9499999999999993</v>
       </c>
       <c r="AC20" s="4" t="str">
         <f ca="1">'Vingio namai XIV'!AA2</f>
@@ -4301,7 +4399,7 @@
         <f>'Vanagupės 36A-204 II'!B3</f>
         <v>46056</v>
       </c>
-      <c r="C21" s="23" t="str">
+      <c r="C21" s="22" t="str">
         <f>'Vanagupės 36A-204 II'!B2</f>
         <v>Vanagupės 36A-204 II</v>
       </c>
@@ -4321,11 +4419,11 @@
         <f>'Vanagupės 36A-204 II'!B11</f>
         <v>103.62</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="11">
         <f>'Vanagupės 36A-204 II'!B12</f>
         <v>46330</v>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="11">
         <f>'Vanagupės 36A-204 II'!R3</f>
         <v>46211</v>
       </c>
@@ -4358,7 +4456,7 @@
         <f>'Namas Panevėžyje'!B3</f>
         <v>46072</v>
       </c>
-      <c r="C22" s="23" t="str">
+      <c r="C22" s="22" t="str">
         <f>'Namas Panevėžyje'!B2</f>
         <v>Namas Panevėžyje</v>
       </c>
@@ -4378,17 +4476,17 @@
         <f>'Namas Panevėžyje'!B11</f>
         <v>157.15</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="11">
         <f>'Namas Panevėžyje'!B12</f>
         <v>46346</v>
       </c>
-      <c r="I22" s="21" t="str">
+      <c r="I22" s="11" t="str">
         <f>'Namas Panevėžyje'!R3</f>
         <v/>
       </c>
       <c r="J22" s="10">
         <f ca="1">'Namas Panevėžyje'!B13</f>
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="K22" s="10" t="str">
         <f ca="1">'Namas Panevėžyje'!S3</f>
@@ -4400,7 +4498,7 @@
       </c>
       <c r="M22" s="4">
         <f>'Namas Panevėžyje'!P3</f>
-        <v>3.78</v>
+        <v>7.08</v>
       </c>
       <c r="AC22" s="4" t="str">
         <f ca="1">'Namas Panevėžyje'!AA2</f>
@@ -4415,7 +4513,7 @@
         <f>'Žemoji 52 XXIX“'!B3</f>
         <v>46073</v>
       </c>
-      <c r="C23" s="23" t="str">
+      <c r="C23" s="22" t="str">
         <f>'Žemoji 52 XXIX“'!B2</f>
         <v>Žemoji 52 XXIX“</v>
       </c>
@@ -4435,11 +4533,11 @@
         <f>'Žemoji 52 XXIX“'!B11</f>
         <v>103.68</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="11">
         <f>'Žemoji 52 XXIX“'!B12</f>
         <v>46220</v>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="11">
         <f>'Žemoji 52 XXIX“'!R3</f>
         <v>46232</v>
       </c>
@@ -4472,7 +4570,7 @@
         <f>'Horizonto 2A XII'!B3</f>
         <v>46091</v>
       </c>
-      <c r="C24" s="23" t="str">
+      <c r="C24" s="22" t="str">
         <f>'Horizonto 2A XII'!B2</f>
         <v>Horizonto 2A XII</v>
       </c>
@@ -4492,21 +4590,21 @@
         <f>'Horizonto 2A XII'!B11</f>
         <v>100</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="11">
         <f>'Horizonto 2A XII'!B12</f>
         <v>46365</v>
       </c>
-      <c r="I24" s="21" t="str">
+      <c r="I24" s="11" t="str">
         <f>'Horizonto 2A XII'!R3</f>
         <v/>
       </c>
       <c r="J24" s="10">
         <f ca="1">'Horizonto 2A XII'!B13</f>
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K24" s="10">
         <f ca="1">'Horizonto 2A XII'!S3</f>
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="L24" s="4">
         <f>'Horizonto 2A XII'!N3</f>
@@ -4529,7 +4627,7 @@
         <f>'Tautvilo kotedžai XIV'!B3</f>
         <v>46088</v>
       </c>
-      <c r="C25" s="23" t="str">
+      <c r="C25" s="22" t="str">
         <f>'Tautvilo kotedžai XIV'!B2</f>
         <v>Tautvilo kotedžai XIV</v>
       </c>
@@ -4549,17 +4647,17 @@
         <f>'Tautvilo kotedžai XIV'!B11</f>
         <v>100</v>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="11">
         <f>'Tautvilo kotedžai XIV'!B12</f>
         <v>46549</v>
       </c>
-      <c r="I25" s="21" t="str">
+      <c r="I25" s="11" t="str">
         <f>'Tautvilo kotedžai XIV'!R3</f>
         <v/>
       </c>
       <c r="J25" s="10">
         <f ca="1">'Tautvilo kotedžai XIV'!B13</f>
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="K25" s="10" t="str">
         <f ca="1">'Tautvilo kotedžai XIV'!S3</f>
@@ -4571,7 +4669,7 @@
       </c>
       <c r="M25" s="4">
         <f>'Tautvilo kotedžai XIV'!P3</f>
-        <v>3.14</v>
+        <v>5.6400000000000006</v>
       </c>
       <c r="AC25" s="4" t="str">
         <f ca="1">'Tautvilo kotedžai XIV'!AA2</f>
@@ -4586,7 +4684,7 @@
         <f>'Kauno 36-118 II'!B3</f>
         <v>46095</v>
       </c>
-      <c r="C26" s="23" t="str">
+      <c r="C26" s="22" t="str">
         <f>'Kauno 36-118 II'!B2</f>
         <v>Kauno 36-118 II</v>
       </c>
@@ -4606,17 +4704,17 @@
         <f>'Kauno 36-118 II'!B11</f>
         <v>102.01</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="11">
         <f>'Kauno 36-118 II'!B12</f>
         <v>46462</v>
       </c>
-      <c r="I26" s="21" t="str">
+      <c r="I26" s="11" t="str">
         <f>'Kauno 36-118 II'!R3</f>
         <v/>
       </c>
       <c r="J26" s="10">
         <f ca="1">'Kauno 36-118 II'!B13</f>
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="K26" s="10" t="str">
         <f ca="1">'Kauno 36-118 II'!S3</f>
@@ -4643,7 +4741,7 @@
         <f>'Vakaro 3A K1 III'!B3</f>
         <v>46211</v>
       </c>
-      <c r="C27" s="23" t="str">
+      <c r="C27" s="22" t="str">
         <f>'Vakaro 3A K1 III'!B2</f>
         <v>Vakaro 3A K1 III</v>
       </c>
@@ -4663,17 +4761,17 @@
         <f>'Vakaro 3A K1 III'!B11</f>
         <v>142.38999999999999</v>
       </c>
-      <c r="H27" s="21">
+      <c r="H27" s="11">
         <f>'Vakaro 3A K1 III'!B12</f>
         <v>46577</v>
       </c>
-      <c r="I27" s="21" t="str">
+      <c r="I27" s="11" t="str">
         <f>'Vakaro 3A K1 III'!R3</f>
         <v/>
       </c>
       <c r="J27" s="10">
         <f ca="1">'Vakaro 3A K1 III'!B13</f>
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="K27" s="10" t="str">
         <f ca="1">'Vakaro 3A K1 III'!S3</f>
@@ -4700,7 +4798,7 @@
         <f>'Užnerio butai XV'!B3</f>
         <v>46232</v>
       </c>
-      <c r="C28" s="23" t="str">
+      <c r="C28" s="22" t="str">
         <f>'Užnerio butai XV'!B2</f>
         <v>Užnerio butai XV</v>
       </c>
@@ -4720,17 +4818,17 @@
         <f>'Užnerio butai XV'!B11</f>
         <v>110.51</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="11">
         <f>'Užnerio butai XV'!B12</f>
         <v>46603</v>
       </c>
-      <c r="I28" s="21" t="str">
+      <c r="I28" s="11" t="str">
         <f>'Užnerio butai XV'!R3</f>
         <v/>
       </c>
       <c r="J28" s="10">
         <f ca="1">'Užnerio butai XV'!B13</f>
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="K28" s="10" t="str">
         <f ca="1">'Užnerio butai XV'!S3</f>
@@ -4744,9 +4842,66 @@
         <f>'Užnerio butai XV'!P3</f>
         <v>0</v>
       </c>
-      <c r="AC28" s="4">
-        <f>'Vakaro 3A K1 III'!AA3</f>
-        <v>0</v>
+      <c r="AC28" s="4" t="str">
+        <f ca="1">'Užnerio butai XV'!AA2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="11">
+        <f>'Vienbutis Gilužiuose III'!B3</f>
+        <v>46267</v>
+      </c>
+      <c r="C29" s="22" t="str">
+        <f>'Vienbutis Gilužiuose III'!B2</f>
+        <v>Vienbutis Gilužiuose III</v>
+      </c>
+      <c r="D29" s="2">
+        <f>'Vienbutis Gilužiuose III'!B8</f>
+        <v>12</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f>'Vienbutis Gilužiuose III'!B5</f>
+        <v>C</v>
+      </c>
+      <c r="F29" s="14">
+        <f>'Vienbutis Gilužiuose III'!B10</f>
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="G29" s="4">
+        <f>'Vienbutis Gilužiuose III'!B11</f>
+        <v>128.59</v>
+      </c>
+      <c r="H29" s="11">
+        <f>'Vienbutis Gilužiuose III'!B12</f>
+        <v>46634</v>
+      </c>
+      <c r="I29" s="11" t="str">
+        <f>'Užnerio butai XV'!R3</f>
+        <v/>
+      </c>
+      <c r="J29" s="10">
+        <f ca="1">'Vienbutis Gilužiuose III'!B13</f>
+        <v>339</v>
+      </c>
+      <c r="K29" s="10" t="str">
+        <f ca="1">'Vienbutis Gilužiuose III'!S3</f>
+        <v/>
+      </c>
+      <c r="L29" s="4">
+        <f>'Vienbutis Gilužiuose III'!N3</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="4">
+        <f>'Vienbutis Gilužiuose III'!P3</f>
+        <v>0</v>
+      </c>
+      <c r="AC29" s="4" t="str">
+        <f ca="1">'Vienbutis Gilužiuose III'!AA2</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -4757,12 +4912,20 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:X1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:M28">
-    <cfRule type="expression" dxfId="105" priority="14">
+  <conditionalFormatting sqref="A3:M29">
+    <cfRule type="expression" dxfId="111" priority="16">
       <formula>AND($G3&gt;0,$G3=$L3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="15">
+    <cfRule type="expression" dxfId="110" priority="17">
       <formula>$AC3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC28">
+    <cfRule type="expression" dxfId="109" priority="1">
+      <formula>AND($G28&gt;0,$G28=$L28)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="2">
+      <formula>$AC28="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -4792,6 +4955,7 @@
     <hyperlink ref="C26" location="'Kauno 36-118 II'!A1" display="'Kauno 36-118 II'!A1" xr:uid="{75F7657E-0901-4A74-80BC-7EA18729A2C1}"/>
     <hyperlink ref="C27" location="'Vakaro 3A K1 III'!A1" display="'Vakaro 3A K1 III'!A1" xr:uid="{89BFE9E6-796F-48DC-A364-A05791FA2A1D}"/>
     <hyperlink ref="C28" location="'Vakaro 3A K1 III'!A1" display="'Vakaro 3A K1 III'!A1" xr:uid="{4C8CFE6A-8D07-4CE1-93FF-AD4D69ED5247}"/>
+    <hyperlink ref="C29" location="'Vakaro 3A K1 III'!A1" display="'Vakaro 3A K1 III'!A1" xr:uid="{78039671-4A3B-408A-9891-7794AE5C4A40}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4799,6 +4963,930 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="11">
+        <v>46174</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>3.78</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>3.78</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="11">
+        <v>46174</v>
+      </c>
+      <c r="K2" s="10">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="Y2" s="11">
+        <f>B4</f>
+        <v>46073</v>
+      </c>
+      <c r="Z2" s="4">
+        <f>B11*-1</f>
+        <v>-157.15</v>
+      </c>
+      <c r="AA2" s="2" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="11">
+        <v>46072</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46265</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11">
+        <v>46268</v>
+      </c>
+      <c r="K3" s="10">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v>3</v>
+      </c>
+      <c r="M3" s="4">
+        <f>B11</f>
+        <v>157.15</v>
+      </c>
+      <c r="N3" s="4">
+        <f>G42</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <f>F42</f>
+        <v>10.050000000000001</v>
+      </c>
+      <c r="P3" s="4">
+        <f>H42+I42</f>
+        <v>7.08</v>
+      </c>
+      <c r="Q3" s="14" t="str">
+        <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
+        <v/>
+      </c>
+      <c r="R3" s="11" t="str">
+        <f>IF(M3=N3,B14,"")</f>
+        <v/>
+      </c>
+      <c r="S3" s="2" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="11">
+        <f>J2</f>
+        <v>46174</v>
+      </c>
+      <c r="Z3" s="4">
+        <f>G2+H2+I2</f>
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="11">
+        <v>46073</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46346</v>
+      </c>
+      <c r="E4" s="4">
+        <v>157.15</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2.97</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y4" s="11">
+        <f t="shared" ref="Y4:Y14" si="1">J3</f>
+        <v>46268</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" ref="Z4:Z14" si="2">G3+H3+I3</f>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y5" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.59</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>9</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="4">
+        <v>157.15</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="20">
+        <v>46346</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="10">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v>51</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="2" t="str">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="8"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D17" s="8"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D18" s="8"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D19" s="8"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D20" s="8"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D21" s="8"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D22" s="8"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D23" s="8"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D24" s="8"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D25" s="8"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D26" s="8"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D27" s="8"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="8"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D29" s="8"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="8"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="8"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D32" s="8"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D33" s="8"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D34" s="8"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D35" s="8"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D36" s="8"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D37" s="8"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D38" s="8"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D39" s="8"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D40" s="8"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D41" s="8"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D42" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="4">
+        <f>SUM(E2:E41)</f>
+        <v>157.15</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
+        <v>10.050000000000001</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="3"/>
+        <v>7.08</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="R1:R2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="79" priority="4">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="5">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="77" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="76" priority="2">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4850,21 +5938,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -4921,9 +6009,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46057</v>
@@ -4953,13 +6041,21 @@
       <c r="F3" s="4">
         <v>2.1800000000000002</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="10" t="str">
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11">
+        <v>46211</v>
+      </c>
+      <c r="K3" s="10">
         <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
-        <v/>
+        <v>-54</v>
       </c>
       <c r="M3" s="4">
         <f>B11</f>
@@ -5032,7 +6128,7 @@
       </c>
       <c r="Y4" s="11">
         <f t="shared" ref="Y4:Y14" si="1">J3</f>
-        <v>0</v>
+        <v>46211</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" ref="Z4:Z14" si="2">G3+H3+I3</f>
@@ -5727,7 +6823,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5776,21 +6872,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -5847,9 +6943,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46055</v>
@@ -5879,13 +6975,21 @@
       <c r="F3" s="4">
         <v>2.9</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="10" t="str">
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11">
+        <v>46267</v>
+      </c>
+      <c r="K3" s="10">
         <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M3" s="4">
         <f>B11</f>
@@ -5901,7 +7005,7 @@
       </c>
       <c r="P3" s="4">
         <f>H42+I42</f>
-        <v>4.05</v>
+        <v>6.9499999999999993</v>
       </c>
       <c r="Q3" s="14" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
@@ -5950,11 +7054,11 @@
       </c>
       <c r="Y4" s="11">
         <f t="shared" ref="Y4:Y14" si="1">J3</f>
-        <v>0</v>
+        <v>46267</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" ref="Z4:Z14" si="2">G3+H3+I3</f>
-        <v>0</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -6185,7 +7289,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -6608,7 +7712,7 @@
       </c>
       <c r="H42" s="4">
         <f t="shared" si="3"/>
-        <v>4.05</v>
+        <v>6.9499999999999993</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="3"/>
@@ -6649,7 +7753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6701,21 +7805,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -6772,9 +7876,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46043</v>
@@ -7600,7 +8704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7649,21 +8753,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -7720,9 +8824,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46013</v>
@@ -7782,7 +8886,7 @@
       </c>
       <c r="P3" s="4">
         <f>H42+I42</f>
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="Q3" s="14" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
@@ -7821,13 +8925,21 @@
       <c r="F4" s="4">
         <v>0.21</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="11">
+        <v>46295</v>
+      </c>
+      <c r="K4" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Y4" s="11">
         <f t="shared" ref="Y4:Y14" si="1">J3</f>
@@ -7864,11 +8976,11 @@
       </c>
       <c r="Y5" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -8066,7 +9178,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -8489,7 +9601,7 @@
       </c>
       <c r="H42" s="4">
         <f t="shared" si="3"/>
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="3"/>
@@ -8530,7 +9642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8579,21 +9691,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -8650,9 +9762,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46003</v>
@@ -8996,7 +10108,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -9460,7 +10572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9509,21 +10621,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -9580,9 +10692,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45967</v>
@@ -9934,7 +11046,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -10398,7 +11510,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -10450,21 +11562,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -10521,9 +11633,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45951</v>
@@ -11335,7 +12447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11384,21 +12496,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -11455,9 +12567,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45916</v>
@@ -11468,7 +12580,7 @@
       </c>
       <c r="AA2" s="2" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -11527,9 +12639,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="2" t="str">
+      <c r="S3" s="2">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
@@ -11809,7 +12921,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>16</v>
+        <v>-14</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -12273,7 +13385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -12325,21 +13437,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -12396,9 +13508,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45917</v>
@@ -13210,8 +14322,352 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:L200"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" style="12" customWidth="1"/>
+    <col min="2" max="4" width="10.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="23"/>
+      <c r="F1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1" s="14">
+        <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
+        <v>0.12084302306175232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>45719</v>
+      </c>
+      <c r="B2" s="4">
+        <v>200</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <f>SUM(B2:B39)</f>
+        <v>1030</v>
+      </c>
+      <c r="G2" s="4">
+        <f>SUM(C2:C39)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <f>SUM(D2:D39)</f>
+        <v>40</v>
+      </c>
+      <c r="I2" s="4">
+        <f>F2-G2</f>
+        <v>1030</v>
+      </c>
+      <c r="K2" s="4">
+        <f>B2*-1</f>
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>45725</v>
+      </c>
+      <c r="B3" s="4">
+        <v>100</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <f t="shared" ref="K3:K17" si="0">B3*-1</f>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>45729</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>10</v>
+      </c>
+      <c r="K4" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
+        <v>45743</v>
+      </c>
+      <c r="B5" s="4">
+        <v>100</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>45757</v>
+      </c>
+      <c r="B6" s="4">
+        <v>100</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>45764</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>10</v>
+      </c>
+      <c r="K7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>45770</v>
+      </c>
+      <c r="B8" s="4">
+        <v>100</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>45791</v>
+      </c>
+      <c r="B9" s="4">
+        <v>100</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>45908</v>
+      </c>
+      <c r="B10" s="4">
+        <v>100</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>45919</v>
+      </c>
+      <c r="B11" s="4">
+        <v>100</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>45957</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4">
+        <v>10</v>
+      </c>
+      <c r="K12" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>46002</v>
+      </c>
+      <c r="B13" s="4">
+        <v>100</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>46010</v>
+      </c>
+      <c r="B14" s="4">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>10</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
+        <v>46095</v>
+      </c>
+      <c r="B15" s="4">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K16" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K17" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" s="12">
+        <f ca="1">TODAY()</f>
+        <v>46295</v>
+      </c>
+      <c r="K200" s="24">
+        <f>Overview!U3</f>
+        <v>1197.8399999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13259,21 +14715,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -13330,9 +14786,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>45908</v>
@@ -13384,7 +14840,7 @@
       </c>
       <c r="N3" s="4">
         <f>G42</f>
-        <v>0</v>
+        <v>123.24</v>
       </c>
       <c r="O3" s="4">
         <f>F42</f>
@@ -13392,15 +14848,15 @@
       </c>
       <c r="P3" s="4">
         <f>H42+I42</f>
-        <v>10.510000000000002</v>
-      </c>
-      <c r="Q3" s="14" t="str">
+        <v>12.740000000000002</v>
+      </c>
+      <c r="Q3" s="14">
         <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
-        <v/>
-      </c>
-      <c r="R3" s="11" t="str">
+        <v>0.10928929448127747</v>
+      </c>
+      <c r="R3" s="11">
         <f>IF(M3=N3,B14,"")</f>
-        <v/>
+        <v>46267</v>
       </c>
       <c r="S3" s="2" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
@@ -13472,13 +14928,21 @@
       <c r="F5" s="4">
         <v>2.48</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G5" s="4">
+        <v>123.24</v>
+      </c>
+      <c r="H5" s="4">
+        <v>2.23</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="11">
+        <v>46267</v>
+      </c>
+      <c r="K5" s="10">
+        <f t="shared" si="0"/>
+        <v>-7</v>
       </c>
       <c r="Y5" s="11">
         <f t="shared" si="1"/>
@@ -13509,11 +14973,11 @@
       </c>
       <c r="Y6" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46267</v>
       </c>
       <c r="Z6" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>125.47</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -13682,9 +15146,9 @@
       <c r="A13" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="10" t="str">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -13710,7 +15174,9 @@
       <c r="A14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="15"/>
+      <c r="B14" s="11">
+        <v>46267</v>
+      </c>
       <c r="D14" s="8"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -13735,9 +15201,9 @@
       <c r="A15" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="2" t="str">
+      <c r="B15" s="2">
         <f>IF(M3=N3,B14-B12,"")</f>
-        <v/>
+        <v>-7</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="4"/>
@@ -14103,11 +15569,11 @@
       </c>
       <c r="G42" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>123.24</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="3"/>
-        <v>10.510000000000002</v>
+        <v>12.740000000000002</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="3"/>
@@ -14148,341 +15614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K200"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.7109375" style="12" customWidth="1"/>
-    <col min="2" max="4" width="10.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
-        <v>45719</v>
-      </c>
-      <c r="B2" s="4">
-        <v>200</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <f>SUM(B2:B39)</f>
-        <v>1030</v>
-      </c>
-      <c r="G2" s="4">
-        <f>SUM(C2:C39)</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <f>SUM(D2:D39)</f>
-        <v>40</v>
-      </c>
-      <c r="I2" s="4">
-        <f>F2-G2</f>
-        <v>1030</v>
-      </c>
-      <c r="K2">
-        <f>B2*-1</f>
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
-        <v>45725</v>
-      </c>
-      <c r="B3" s="4">
-        <v>100</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K17" si="0">B3*-1</f>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>45729</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>10</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
-        <v>45743</v>
-      </c>
-      <c r="B5" s="4">
-        <v>100</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
-        <v>45757</v>
-      </c>
-      <c r="B6" s="4">
-        <v>100</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <v>45764</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>45770</v>
-      </c>
-      <c r="B8" s="4">
-        <v>100</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
-        <v>45791</v>
-      </c>
-      <c r="B9" s="4">
-        <v>100</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>45908</v>
-      </c>
-      <c r="B10" s="4">
-        <v>100</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
-        <v>45919</v>
-      </c>
-      <c r="B11" s="4">
-        <v>100</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>45957</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>10</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>46002</v>
-      </c>
-      <c r="B13" s="4">
-        <v>100</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>46010</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0</v>
-      </c>
-      <c r="C14" s="4">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
-        <v>10</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
-        <v>46095</v>
-      </c>
-      <c r="B15" s="4">
-        <v>30</v>
-      </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="0"/>
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A200" s="12">
-        <f ca="1">TODAY()</f>
-        <v>46265</v>
-      </c>
-      <c r="K200" s="25">
-        <f>Overview!U3</f>
-        <v>1186.7</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -14534,21 +15666,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -14605,9 +15737,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45791</v>
@@ -15405,7 +16537,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -15457,21 +16589,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -15528,9 +16660,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45770</v>
@@ -16356,7 +17488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -16408,21 +17540,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -16479,9 +17611,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45764</v>
@@ -17321,7 +18453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -17373,21 +18505,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -17444,9 +18576,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45757</v>
@@ -18243,7 +19375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -18295,21 +19427,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -18366,9 +19498,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45743</v>
@@ -19207,7 +20339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -19259,21 +20391,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -19330,9 +20462,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45729</v>
@@ -20359,7 +21491,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -20411,21 +21543,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -20482,9 +21614,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45725</v>
@@ -21512,7 +22644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -21564,21 +22696,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -21635,9 +22767,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45721</v>
@@ -22646,8 +23778,8 @@
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-      <c r="Y42" s="26"/>
-      <c r="Z42" s="27"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -22681,7 +23813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -22733,21 +23865,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -22804,9 +23936,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45719</v>
@@ -23815,8 +24947,8 @@
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-      <c r="Y42" s="26"/>
-      <c r="Z42" s="27"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -23851,6 +24983,920 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAC2403A-A6E9-4CD3-8B0F-3660A657E5EF}">
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="11">
+        <v>46387</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="10" t="str">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v/>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="Y2" s="11">
+        <f>B4</f>
+        <v>46269</v>
+      </c>
+      <c r="Z2" s="4">
+        <f>B11*-1</f>
+        <v>-128.59</v>
+      </c>
+      <c r="AA2" s="2" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="11">
+        <v>46267</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46477</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>3.05</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="10" t="str">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="4">
+        <f>B11</f>
+        <v>128.59</v>
+      </c>
+      <c r="N3" s="4">
+        <f>G42</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <f>F42</f>
+        <v>12.27</v>
+      </c>
+      <c r="P3" s="4">
+        <f>H42+I42</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="14" t="str">
+        <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
+        <v/>
+      </c>
+      <c r="R3" s="11" t="str">
+        <f>IF(M3=N3,B14,"")</f>
+        <v/>
+      </c>
+      <c r="S3" s="2" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="11">
+        <f>J2</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
+        <f>G2+H2+I2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="11">
+        <v>46269</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46568</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>3.05</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y4" s="11">
+        <f t="shared" ref="Y4:Y14" si="1">J3</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" ref="Z4:Z14" si="2">G3+H3+I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="11">
+        <v>46634</v>
+      </c>
+      <c r="E5" s="4">
+        <v>128.59</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2.17</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y5" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>12</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="4">
+        <v>128.59</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46634</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="10">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v>339</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="2" t="str">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="8"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D17" s="8"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D18" s="8"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D19" s="8"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D20" s="8"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D21" s="8"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D22" s="8"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D23" s="8"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D24" s="8"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D25" s="8"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D26" s="8"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D27" s="8"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="8"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D29" s="8"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="8"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="8"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D32" s="8"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D33" s="8"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D34" s="8"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D35" s="8"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D36" s="8"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D37" s="8"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D38" s="8"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D39" s="8"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D40" s="8"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D41" s="8"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D42" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="4">
+        <f>SUM(E2:E41)</f>
+        <v>128.59</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
+        <v>12.27</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="107" priority="3">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="4">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="105" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="104" priority="2">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD1A0671-14D9-4590-9CB7-560703BB8637}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23899,21 +25945,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -23962,9 +26008,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46238</v>
@@ -24271,7 +26317,7 @@
       <c r="A12" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="11">
         <v>46603</v>
       </c>
       <c r="D12" s="11"/>
@@ -24300,7 +26346,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="4"/>
@@ -24764,7 +26810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D1DFE8-4730-46B9-AA04-8B9A813ABE1E}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -24813,21 +26859,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -24876,9 +26922,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46212</v>
@@ -25214,7 +27260,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -25678,7 +27724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -25727,21 +27773,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -25798,9 +27844,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46097</v>
@@ -26136,7 +28182,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -26600,7 +28646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -26649,21 +28695,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -26720,9 +28766,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46092</v>
@@ -26752,13 +28798,21 @@
       <c r="F3" s="4">
         <v>2.5</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="10" t="str">
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11">
+        <v>46295</v>
+      </c>
+      <c r="K3" s="10">
         <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M3" s="4">
         <f>B11</f>
@@ -26774,7 +28828,7 @@
       </c>
       <c r="P3" s="4">
         <f>H42+I42</f>
-        <v>3.14</v>
+        <v>5.6400000000000006</v>
       </c>
       <c r="Q3" s="14" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
@@ -26823,11 +28877,11 @@
       </c>
       <c r="Y4" s="11">
         <f t="shared" ref="Y4:Y14" si="1">J3</f>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" ref="Z4:Z14" si="2">G3+H3+I3</f>
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -27064,7 +29118,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -27487,7 +29541,7 @@
       </c>
       <c r="H42" s="4">
         <f t="shared" si="3"/>
-        <v>3.14</v>
+        <v>5.6400000000000006</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" si="3"/>
@@ -27528,8 +29582,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -27577,21 +29634,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -27640,9 +29697,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46091</v>
@@ -27706,7 +29763,7 @@
       </c>
       <c r="S3" s="2">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
@@ -27972,7 +30029,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="15"/>
@@ -28436,7 +30493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -28488,21 +30545,21 @@
       <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="29"/>
+      <c r="O1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="32" t="s">
         <v>84</v>
       </c>
       <c r="Y1" s="17" t="s">
@@ -28559,9 +30616,9 @@
       <c r="P2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="11">
         <f>B4</f>
         <v>46073</v>
@@ -29357,920 +31414,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:AA42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
-    <col min="5" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" customWidth="1"/>
-    <col min="13" max="19" width="10.7109375" customWidth="1"/>
-    <col min="20" max="24" width="8.7109375" customWidth="1"/>
-    <col min="25" max="27" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="R1" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="S1" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z1" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA1" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="11">
-        <v>46174</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>3.78</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <v>3.78</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="11">
-        <v>46174</v>
-      </c>
-      <c r="K2" s="10">
-        <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="Y2" s="11">
-        <f>B4</f>
-        <v>46073</v>
-      </c>
-      <c r="Z2" s="4">
-        <f>B11*-1</f>
-        <v>-157.15</v>
-      </c>
-      <c r="AA2" s="2" t="str">
-        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="11">
-        <v>46072</v>
-      </c>
-      <c r="D3" s="11">
-        <v>46265</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="10" t="str">
-        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="M3" s="4">
-        <f>B11</f>
-        <v>157.15</v>
-      </c>
-      <c r="N3" s="4">
-        <f>G42</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="4">
-        <f>F42</f>
-        <v>10.050000000000001</v>
-      </c>
-      <c r="P3" s="4">
-        <f>H42+I42</f>
-        <v>3.78</v>
-      </c>
-      <c r="Q3" s="14" t="str">
-        <f>IF(M3=N3,XIRR(Z2:Z14,Y2:Y14),"")</f>
-        <v/>
-      </c>
-      <c r="R3" s="11" t="str">
-        <f>IF(M3=N3,B14,"")</f>
-        <v/>
-      </c>
-      <c r="S3" s="2" t="str">
-        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
-      </c>
-      <c r="Y3" s="11">
-        <f>J2</f>
-        <v>46174</v>
-      </c>
-      <c r="Z3" s="4">
-        <f>G2+H2+I2</f>
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="11">
-        <v>46073</v>
-      </c>
-      <c r="D4" s="11">
-        <v>46346</v>
-      </c>
-      <c r="E4" s="4">
-        <v>157.15</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2.97</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y4" s="11">
-        <f t="shared" ref="Y4:Y14" si="1">J3</f>
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4">
-        <f t="shared" ref="Z4:Z14" si="2">G3+H3+I3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y5" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0.24</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y6" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.59</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y7" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z7" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="2">
-        <v>9</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y8" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y9" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z9" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="14">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y10" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="4">
-        <v>157.15</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y11" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="20">
-        <v>46346</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y12" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="10">
-        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>81</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y13" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y14" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" s="2" t="str">
-        <f>IF(M3=N3,B14-B12,"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="8"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D17" s="8"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D18" s="8"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D19" s="8"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D20" s="8"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D21" s="8"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D22" s="8"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D23" s="8"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D24" s="8"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D25" s="8"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D26" s="8"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D27" s="8"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D28" s="8"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D29" s="8"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D30" s="8"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D31" s="8"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D32" s="8"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D33" s="8"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D34" s="8"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D35" s="8"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D36" s="8"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D37" s="8"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D38" s="8"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D39" s="8"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D40" s="8"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D41" s="8"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D42" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="4">
-        <f>SUM(E2:E41)</f>
-        <v>157.15</v>
-      </c>
-      <c r="F42" s="4">
-        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
-        <v>10.050000000000001</v>
-      </c>
-      <c r="G42" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="4">
-        <f t="shared" si="3"/>
-        <v>3.78</v>
-      </c>
-      <c r="I42" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="R1:R2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="79" priority="4">
-      <formula>$M$3=$N$3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="5">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="77" priority="1">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="76" priority="2">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>